--- a/data/processed/harmonization/Carbon__Total_carbon/10.15485_1631979/10.15485_1631979_soil_Carbon__Total_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Total_carbon/10.15485_1631979/10.15485_1631979_soil_Carbon__Total_carbon.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -549,7 +549,7 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -597,7 +597,7 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -645,7 +645,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -681,7 +681,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -693,7 +693,7 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -729,7 +729,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -741,7 +741,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -789,7 +789,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -837,7 +837,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -885,7 +885,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -933,7 +933,7 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -981,7 +981,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1029,7 +1029,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1077,7 +1077,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1125,7 +1125,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1173,7 +1173,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1221,7 +1221,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1269,7 +1269,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1317,7 +1317,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1365,7 +1365,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1413,7 +1413,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1461,7 +1461,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1509,7 +1509,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1557,7 +1557,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1605,7 +1605,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1653,7 +1653,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1701,7 +1701,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1749,7 +1749,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -1797,7 +1797,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -1845,7 +1845,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1893,7 +1893,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1941,7 +1941,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -1989,7 +1989,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2037,7 +2037,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2085,7 +2085,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2133,7 +2133,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2181,7 +2181,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2229,7 +2229,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2277,7 +2277,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2325,7 +2325,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2373,7 +2373,7 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2421,7 +2421,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2469,7 +2469,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2517,7 +2517,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2565,7 +2565,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2613,7 +2613,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2661,7 +2661,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2709,7 +2709,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -2757,7 +2757,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -2805,7 +2805,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -2853,7 +2853,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -2901,7 +2901,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -2949,7 +2949,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -2997,7 +2997,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3045,7 +3045,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3093,7 +3093,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3141,7 +3141,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3189,7 +3189,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3237,7 +3237,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3285,7 +3285,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3333,7 +3333,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3381,7 +3381,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3429,7 +3429,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3477,7 +3477,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3525,7 +3525,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3573,7 +3573,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3621,7 +3621,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3669,7 +3669,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -3717,7 +3717,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -3765,7 +3765,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -3813,7 +3813,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -3861,7 +3861,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -3909,7 +3909,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -3957,7 +3957,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4005,7 +4005,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4053,7 +4053,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4101,7 +4101,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4149,7 +4149,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4197,7 +4197,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4245,7 +4245,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4293,7 +4293,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4341,7 +4341,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -4389,7 +4389,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -4437,7 +4437,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -4485,7 +4485,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4533,7 +4533,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -4581,7 +4581,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -4629,7 +4629,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -4677,7 +4677,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -4725,7 +4725,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -4773,7 +4773,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -4821,7 +4821,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -4869,7 +4869,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -4917,7 +4917,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -4965,7 +4965,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:WF_SFA_Genomic_Sampling_Sites___East_River_Watershed_Floodplain__Co.kml (KML placemark); data key Sample ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5013,7 +5013,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5061,7 +5061,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5109,7 +5109,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5157,7 +5157,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5205,7 +5205,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5253,7 +5253,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -5301,7 +5301,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5349,7 +5349,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5397,7 +5397,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5445,7 +5445,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5493,7 +5493,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5541,7 +5541,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5589,7 +5589,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -5637,7 +5637,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -5685,7 +5685,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -5733,7 +5733,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -5781,7 +5781,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -5829,7 +5829,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -5877,7 +5877,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -5925,7 +5925,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -5973,7 +5973,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6009,7 +6009,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6021,7 +6021,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6069,7 +6069,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6117,7 +6117,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6165,7 +6165,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6213,7 +6213,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6249,7 +6249,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6261,7 +6261,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6309,7 +6309,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6345,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>dry_combustion</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -6357,7 +6357,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage</t>
+          <t>lat/long source: doi:10.15485/1631979:FloodplainSamplingSites_PMatheus_BanfieldLab__1_.xlsx [2016] (joined on Sample ID); data key Samples ID; source column Average (%, unit from group header); date 2015-09 from package temporal coverage; method from cited paper doi:10.1186/s40168-020-00957-z</t>
         </is>
       </c>
     </row>
